--- a/demo/7_출력검사_리포트_최종본.xlsx
+++ b/demo/7_출력검사_리포트_최종본.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,6 +569,18 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>공유 범위</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>대외비 — 사내 개발팀 한정. 외부 공유 금지</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
